--- a/Best ch pipeline/original_best_channels_stat_18m_hammer.xlsx
+++ b/Best ch pipeline/original_best_channels_stat_18m_hammer.xlsx
@@ -1803,12 +1803,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ch_1</t>
+          <t>ch_0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ch_0</t>
+          <t>ch_1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1817,46 +1817,46 @@
         </is>
       </c>
       <c r="H18" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" t="n">
         <v>27</v>
-      </c>
-      <c r="I18" t="n">
-        <v>34</v>
       </c>
       <c r="J18" t="n">
         <v>20</v>
       </c>
       <c r="K18" t="n">
+        <v>13</v>
+      </c>
+      <c r="L18" t="n">
         <v>9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>13</v>
       </c>
       <c r="M18" t="n">
         <v>10</v>
       </c>
       <c r="N18" t="n">
+        <v>1090.781649530222</v>
+      </c>
+      <c r="O18" t="n">
         <v>1361.430638929279</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1090.781649530222</v>
       </c>
       <c r="P18" t="n">
         <v>1499.933306412059</v>
       </c>
       <c r="Q18" t="n">
+        <v>853.6176470588235</v>
+      </c>
+      <c r="R18" t="n">
         <v>1029</v>
-      </c>
-      <c r="R18" t="n">
-        <v>853.6176470588235</v>
       </c>
       <c r="S18" t="n">
         <v>1389.15</v>
       </c>
       <c r="T18" t="n">
+        <v>408</v>
+      </c>
+      <c r="U18" t="n">
         <v>426</v>
-      </c>
-      <c r="U18" t="n">
-        <v>408</v>
       </c>
       <c r="V18" t="n">
         <v>644.5</v>
@@ -6964,58 +6964,58 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ch_2</t>
+          <t>ch_1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ch_1</t>
+          <t>ch_2</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>27</v>
       </c>
       <c r="I18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" t="n">
         <v>21</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23</v>
       </c>
       <c r="K18" t="n">
         <v>15</v>
       </c>
       <c r="L18" t="n">
+        <v>13</v>
+      </c>
+      <c r="M18" t="n">
         <v>15</v>
-      </c>
-      <c r="M18" t="n">
-        <v>13</v>
       </c>
       <c r="N18" t="n">
         <v>922.4125140921745</v>
       </c>
       <c r="O18" t="n">
+        <v>1079.1936145602</v>
+      </c>
+      <c r="P18" t="n">
         <v>1078.451091678643</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1079.1936145602</v>
       </c>
       <c r="Q18" t="n">
         <v>1017</v>
       </c>
       <c r="R18" t="n">
+        <v>1128.695652173913</v>
+      </c>
+      <c r="S18" t="n">
         <v>1213.571428571429</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1128.695652173913</v>
       </c>
       <c r="T18" t="n">
         <v>727</v>
       </c>
       <c r="U18" t="n">
+        <v>727</v>
+      </c>
+      <c r="V18" t="n">
         <v>824</v>
-      </c>
-      <c r="V18" t="n">
-        <v>727</v>
       </c>
     </row>
     <row r="19">
